--- a/pasto_case/results/AHP_results/matrix_normalized.xlsx
+++ b/pasto_case/results/AHP_results/matrix_normalized.xlsx
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.576</v>
+        <v>0.777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.292</v>
+        <v>0.416</v>
       </c>
       <c r="F2" t="n">
-        <v>0.277</v>
+        <v>0.389</v>
       </c>
       <c r="G2" t="n">
-        <v>0.192</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J2" t="n">
-        <v>0.165</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="3">
@@ -548,25 +548,25 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.134</v>
+        <v>0.215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.127</v>
+        <v>0.201</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.081</v>
+        <v>0.114</v>
       </c>
       <c r="I3" t="n">
-        <v>0.074</v>
+        <v>0.106</v>
       </c>
       <c r="J3" t="n">
-        <v>0.073</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="4">
@@ -577,28 +577,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.555</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F4" t="n">
-        <v>0.266</v>
+        <v>0.376</v>
       </c>
       <c r="G4" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.173</v>
+        <v>0.212</v>
       </c>
       <c r="I4" t="n">
-        <v>0.16</v>
+        <v>0.198</v>
       </c>
       <c r="J4" t="n">
-        <v>0.159</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="5">
@@ -609,28 +609,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.569</v>
+        <v>0.768</v>
       </c>
       <c r="E5" t="n">
-        <v>0.288</v>
+        <v>0.411</v>
       </c>
       <c r="F5" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G5" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.177</v>
+        <v>0.217</v>
       </c>
       <c r="I5" t="n">
-        <v>0.164</v>
+        <v>0.203</v>
       </c>
       <c r="J5" t="n">
-        <v>0.163</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="6">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.528</v>
+        <v>0.718</v>
       </c>
       <c r="E6" t="n">
-        <v>0.266</v>
+        <v>0.384</v>
       </c>
       <c r="F6" t="n">
-        <v>0.253</v>
+        <v>0.359</v>
       </c>
       <c r="G6" t="n">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.164</v>
+        <v>0.203</v>
       </c>
       <c r="I6" t="n">
-        <v>0.151</v>
+        <v>0.189</v>
       </c>
       <c r="J6" t="n">
-        <v>0.15</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="7">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.533</v>
+        <v>0.723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.269</v>
+        <v>0.387</v>
       </c>
       <c r="F7" t="n">
-        <v>0.255</v>
+        <v>0.362</v>
       </c>
       <c r="G7" t="n">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I7" t="n">
-        <v>0.153</v>
+        <v>0.191</v>
       </c>
       <c r="J7" t="n">
-        <v>0.152</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="8">
@@ -705,28 +705,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.574</v>
+        <v>0.775</v>
       </c>
       <c r="E8" t="n">
-        <v>0.291</v>
+        <v>0.415</v>
       </c>
       <c r="F8" t="n">
-        <v>0.276</v>
+        <v>0.388</v>
       </c>
       <c r="G8" t="n">
-        <v>0.192</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.18</v>
+        <v>0.219</v>
       </c>
       <c r="I8" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J8" t="n">
-        <v>0.165</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="9">
@@ -737,28 +737,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.577</v>
+        <v>0.778</v>
       </c>
       <c r="E9" t="n">
-        <v>0.292</v>
+        <v>0.416</v>
       </c>
       <c r="F9" t="n">
-        <v>0.277</v>
+        <v>0.389</v>
       </c>
       <c r="G9" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="I9" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J9" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="10">
@@ -773,28 +773,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.304</v>
+        <v>0.433</v>
       </c>
       <c r="E10" t="n">
-        <v>0.304</v>
+        <v>0.433</v>
       </c>
       <c r="F10" t="n">
-        <v>0.296</v>
+        <v>0.414</v>
       </c>
       <c r="G10" t="n">
-        <v>0.216</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.17</v>
+        <v>0.209</v>
       </c>
       <c r="I10" t="n">
-        <v>0.17</v>
+        <v>0.209</v>
       </c>
       <c r="J10" t="n">
-        <v>0.17</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="11">
@@ -805,28 +805,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E11" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F11" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G11" t="n">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
       <c r="I11" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
       <c r="J11" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="12">
@@ -837,28 +837,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E12" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F12" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G12" t="n">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
       <c r="I12" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
       <c r="J12" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="13">
@@ -869,28 +869,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E13" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F13" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G13" t="n">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
       <c r="I13" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
       <c r="J13" t="n">
-        <v>0.156</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="14">
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.248</v>
+        <v>0.371</v>
       </c>
       <c r="E14" t="n">
-        <v>0.248</v>
+        <v>0.371</v>
       </c>
       <c r="F14" t="n">
-        <v>0.241</v>
+        <v>0.355</v>
       </c>
       <c r="G14" t="n">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.137</v>
+        <v>0.179</v>
       </c>
       <c r="I14" t="n">
-        <v>0.137</v>
+        <v>0.179</v>
       </c>
       <c r="J14" t="n">
-        <v>0.137</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="15">
@@ -933,28 +933,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.297</v>
+        <v>0.423</v>
       </c>
       <c r="E15" t="n">
-        <v>0.297</v>
+        <v>0.423</v>
       </c>
       <c r="F15" t="n">
-        <v>0.29</v>
+        <v>0.405</v>
       </c>
       <c r="G15" t="n">
-        <v>0.211</v>
+        <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I15" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J15" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="16">
@@ -965,28 +965,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.297</v>
+        <v>0.423</v>
       </c>
       <c r="E16" t="n">
-        <v>0.297</v>
+        <v>0.423</v>
       </c>
       <c r="F16" t="n">
-        <v>0.29</v>
+        <v>0.405</v>
       </c>
       <c r="G16" t="n">
-        <v>0.211</v>
+        <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I16" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J16" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="17">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.297</v>
+        <v>0.423</v>
       </c>
       <c r="E17" t="n">
-        <v>0.297</v>
+        <v>0.423</v>
       </c>
       <c r="F17" t="n">
-        <v>0.29</v>
+        <v>0.405</v>
       </c>
       <c r="G17" t="n">
-        <v>0.211</v>
+        <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I17" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J17" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="18">
@@ -1033,28 +1033,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.116</v>
+        <v>0.156</v>
       </c>
       <c r="E18" t="n">
-        <v>0.116</v>
+        <v>0.156</v>
       </c>
       <c r="F18" t="n">
-        <v>0.117</v>
+        <v>0.156</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.125</v>
+        <v>0.157</v>
       </c>
       <c r="I18" t="n">
-        <v>0.125</v>
+        <v>0.157</v>
       </c>
       <c r="J18" t="n">
-        <v>0.125</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="19">
@@ -1065,28 +1065,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.185</v>
+        <v>0.001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E19" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F19" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="G19" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.287</v>
+        <v>0.402</v>
       </c>
       <c r="I19" t="n">
-        <v>0.287</v>
+        <v>0.402</v>
       </c>
       <c r="J19" t="n">
-        <v>0.287</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="20">
@@ -1097,28 +1097,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.185</v>
+        <v>0.001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E20" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F20" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="G20" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.287</v>
+        <v>0.402</v>
       </c>
       <c r="I20" t="n">
-        <v>0.287</v>
+        <v>0.402</v>
       </c>
       <c r="J20" t="n">
-        <v>0.287</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="21">
@@ -1129,28 +1129,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.179</v>
+        <v>0.001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="E21" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="F21" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G21" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.279</v>
+        <v>0.384</v>
       </c>
       <c r="I21" t="n">
-        <v>0.279</v>
+        <v>0.384</v>
       </c>
       <c r="J21" t="n">
-        <v>0.28</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="22">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.745</v>
+        <v>0.002</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1193,28 +1193,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="E23" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="F23" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="G23" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I23" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J23" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="24">
@@ -1225,28 +1225,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="E24" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="F24" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="G24" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I24" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J24" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="25">
@@ -1257,28 +1257,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="E25" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="F25" t="n">
-        <v>0.158</v>
+        <v>0.204</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I25" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J25" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="26">
@@ -1293,28 +1293,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="G26" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.006</v>
+        <v>0.029</v>
       </c>
       <c r="I26" t="n">
-        <v>0.006</v>
+        <v>0.029</v>
       </c>
       <c r="J26" t="n">
-        <v>0.006</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="27">
@@ -1325,28 +1325,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.003</v>
       </c>
       <c r="D27" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E27" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F27" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G27" t="n">
-        <v>0.585</v>
+        <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
       <c r="I27" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
       <c r="J27" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="28">
@@ -1357,28 +1357,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.003</v>
       </c>
       <c r="D28" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E28" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F28" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G28" t="n">
-        <v>0.585</v>
+        <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
       <c r="I28" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
       <c r="J28" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="29">
@@ -1389,28 +1389,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.003</v>
       </c>
       <c r="D29" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E29" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F29" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G29" t="n">
-        <v>0.585</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
       <c r="I29" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
       <c r="J29" t="n">
-        <v>0.261</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="30">
@@ -1421,28 +1421,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.293</v>
+        <v>0.002</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.223</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.223</v>
       </c>
       <c r="F30" t="n">
-        <v>0.068</v>
+        <v>0.214</v>
       </c>
       <c r="G30" t="n">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.146</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.146</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="31">
@@ -1453,28 +1453,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.646</v>
+        <v>0.003</v>
       </c>
       <c r="D31" t="n">
-        <v>0.175</v>
+        <v>0.312</v>
       </c>
       <c r="E31" t="n">
-        <v>0.175</v>
+        <v>0.312</v>
       </c>
       <c r="F31" t="n">
-        <v>0.171</v>
+        <v>0.299</v>
       </c>
       <c r="G31" t="n">
-        <v>0.38</v>
+        <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I31" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J31" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="32">
@@ -1485,28 +1485,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.646</v>
+        <v>0.003</v>
       </c>
       <c r="D32" t="n">
-        <v>0.175</v>
+        <v>0.312</v>
       </c>
       <c r="E32" t="n">
-        <v>0.175</v>
+        <v>0.312</v>
       </c>
       <c r="F32" t="n">
-        <v>0.171</v>
+        <v>0.299</v>
       </c>
       <c r="G32" t="n">
-        <v>0.38</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I32" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J32" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="33">
@@ -1517,28 +1517,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.646</v>
+        <v>0.003</v>
       </c>
       <c r="D33" t="n">
-        <v>0.175</v>
+        <v>0.312</v>
       </c>
       <c r="E33" t="n">
-        <v>0.175</v>
+        <v>0.312</v>
       </c>
       <c r="F33" t="n">
-        <v>0.171</v>
+        <v>0.299</v>
       </c>
       <c r="G33" t="n">
-        <v>0.38</v>
+        <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I33" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J33" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="34">
@@ -1553,19 +1553,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1585,28 +1585,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.653</v>
+        <v>0.647</v>
       </c>
       <c r="D35" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E35" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F35" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8</v>
+        <v>0.648</v>
       </c>
       <c r="H35" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="I35" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="J35" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="36">
@@ -1617,28 +1617,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.653</v>
+        <v>0.647</v>
       </c>
       <c r="D36" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E36" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F36" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8</v>
+        <v>0.648</v>
       </c>
       <c r="H36" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="I36" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="J36" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="37">
@@ -1649,28 +1649,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.653</v>
+        <v>0.647</v>
       </c>
       <c r="D37" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="E37" t="n">
-        <v>0.281</v>
+        <v>0.402</v>
       </c>
       <c r="F37" t="n">
-        <v>0.273</v>
+        <v>0.384</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8</v>
+        <v>0.648</v>
       </c>
       <c r="H37" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="I37" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="J37" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="38">
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1713,28 +1713,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.357</v>
+        <v>0.62</v>
       </c>
       <c r="E39" t="n">
-        <v>0.357</v>
+        <v>0.62</v>
       </c>
       <c r="F39" t="n">
-        <v>0.347</v>
+        <v>0.594</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I39" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J39" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="40">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.357</v>
+        <v>0.62</v>
       </c>
       <c r="E40" t="n">
-        <v>0.357</v>
+        <v>0.62</v>
       </c>
       <c r="F40" t="n">
-        <v>0.347</v>
+        <v>0.594</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I40" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J40" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="41">
@@ -1777,28 +1777,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.357</v>
+        <v>0.62</v>
       </c>
       <c r="E41" t="n">
-        <v>0.357</v>
+        <v>0.62</v>
       </c>
       <c r="F41" t="n">
-        <v>0.347</v>
+        <v>0.594</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="I41" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
       <c r="J41" t="n">
-        <v>0.166</v>
+        <v>0.205</v>
       </c>
     </row>
   </sheetData>

--- a/pasto_case/results/AHP_results/matrix_normalized.xlsx
+++ b/pasto_case/results/AHP_results/matrix_normalized.xlsx
@@ -462,42 +462,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
     </row>
@@ -509,256 +509,256 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D2" t="n">
-        <v>0.777</v>
+        <v>0.766</v>
       </c>
       <c r="E2" t="n">
-        <v>0.416</v>
+        <v>0.389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.389</v>
+        <v>0.362</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="H2" t="n">
-        <v>0.22</v>
+        <v>0.196</v>
       </c>
       <c r="I2" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J2" t="n">
-        <v>0.204</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.215</v>
+        <v>0.178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.201</v>
+        <v>0.166</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="H3" t="n">
-        <v>0.114</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.106</v>
+        <v>0.079</v>
       </c>
       <c r="J3" t="n">
-        <v>0.106</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>0.739</v>
       </c>
       <c r="E4" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F4" t="n">
-        <v>0.376</v>
+        <v>0.348</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="H4" t="n">
-        <v>0.212</v>
+        <v>0.189</v>
       </c>
       <c r="I4" t="n">
-        <v>0.198</v>
+        <v>0.174</v>
       </c>
       <c r="J4" t="n">
-        <v>0.197</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="D5" t="n">
-        <v>0.768</v>
+        <v>0.757</v>
       </c>
       <c r="E5" t="n">
-        <v>0.411</v>
+        <v>0.384</v>
       </c>
       <c r="F5" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="H5" t="n">
-        <v>0.217</v>
+        <v>0.194</v>
       </c>
       <c r="I5" t="n">
-        <v>0.203</v>
+        <v>0.179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.202</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D6" t="n">
-        <v>0.718</v>
+        <v>0.705</v>
       </c>
       <c r="E6" t="n">
-        <v>0.384</v>
+        <v>0.356</v>
       </c>
       <c r="F6" t="n">
-        <v>0.359</v>
+        <v>0.331</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="H6" t="n">
-        <v>0.203</v>
+        <v>0.179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.189</v>
+        <v>0.165</v>
       </c>
       <c r="J6" t="n">
-        <v>0.189</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="D7" t="n">
-        <v>0.723</v>
+        <v>0.71</v>
       </c>
       <c r="E7" t="n">
-        <v>0.387</v>
+        <v>0.358</v>
       </c>
       <c r="F7" t="n">
-        <v>0.362</v>
+        <v>0.333</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.201</v>
       </c>
       <c r="H7" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I7" t="n">
-        <v>0.191</v>
+        <v>0.166</v>
       </c>
       <c r="J7" t="n">
-        <v>0.19</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D8" t="n">
-        <v>0.775</v>
+        <v>0.765</v>
       </c>
       <c r="E8" t="n">
-        <v>0.415</v>
+        <v>0.388</v>
       </c>
       <c r="F8" t="n">
-        <v>0.388</v>
+        <v>0.361</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="H8" t="n">
-        <v>0.219</v>
+        <v>0.196</v>
       </c>
       <c r="I8" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J8" t="n">
-        <v>0.204</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D9" t="n">
-        <v>0.778</v>
+        <v>0.768</v>
       </c>
       <c r="E9" t="n">
-        <v>0.416</v>
+        <v>0.389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.389</v>
+        <v>0.362</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="H9" t="n">
-        <v>0.22</v>
+        <v>0.197</v>
       </c>
       <c r="I9" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J9" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="10">
@@ -769,256 +769,256 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D10" t="n">
-        <v>0.433</v>
+        <v>0.407</v>
       </c>
       <c r="E10" t="n">
-        <v>0.433</v>
+        <v>0.407</v>
       </c>
       <c r="F10" t="n">
-        <v>0.414</v>
+        <v>0.389</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001</v>
+        <v>0.239</v>
       </c>
       <c r="H10" t="n">
-        <v>0.209</v>
+        <v>0.185</v>
       </c>
       <c r="I10" t="n">
-        <v>0.209</v>
+        <v>0.185</v>
       </c>
       <c r="J10" t="n">
-        <v>0.209</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D11" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E11" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="H11" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="I11" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="J11" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D12" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E12" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F12" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="H12" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="J12" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D13" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E13" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F13" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="H13" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D14" t="n">
-        <v>0.371</v>
+        <v>0.341</v>
       </c>
       <c r="E14" t="n">
-        <v>0.371</v>
+        <v>0.341</v>
       </c>
       <c r="F14" t="n">
-        <v>0.355</v>
+        <v>0.326</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="H14" t="n">
-        <v>0.179</v>
+        <v>0.154</v>
       </c>
       <c r="I14" t="n">
-        <v>0.179</v>
+        <v>0.154</v>
       </c>
       <c r="J14" t="n">
-        <v>0.179</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="D15" t="n">
-        <v>0.423</v>
+        <v>0.397</v>
       </c>
       <c r="E15" t="n">
-        <v>0.423</v>
+        <v>0.397</v>
       </c>
       <c r="F15" t="n">
-        <v>0.405</v>
+        <v>0.379</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001</v>
+        <v>0.233</v>
       </c>
       <c r="H15" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I15" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J15" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="D16" t="n">
-        <v>0.423</v>
+        <v>0.397</v>
       </c>
       <c r="E16" t="n">
-        <v>0.423</v>
+        <v>0.397</v>
       </c>
       <c r="F16" t="n">
-        <v>0.405</v>
+        <v>0.379</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001</v>
+        <v>0.233</v>
       </c>
       <c r="H16" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I16" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J16" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="D17" t="n">
-        <v>0.423</v>
+        <v>0.397</v>
       </c>
       <c r="E17" t="n">
-        <v>0.423</v>
+        <v>0.397</v>
       </c>
       <c r="F17" t="n">
-        <v>0.405</v>
+        <v>0.379</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001</v>
+        <v>0.233</v>
       </c>
       <c r="H17" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I17" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J17" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="18">
@@ -1029,139 +1029,139 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D18" t="n">
-        <v>0.156</v>
+        <v>0.117</v>
       </c>
       <c r="E18" t="n">
-        <v>0.156</v>
+        <v>0.117</v>
       </c>
       <c r="F18" t="n">
-        <v>0.156</v>
+        <v>0.119</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.157</v>
+        <v>0.131</v>
       </c>
       <c r="I18" t="n">
-        <v>0.157</v>
+        <v>0.131</v>
       </c>
       <c r="J18" t="n">
-        <v>0.156</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001</v>
+        <v>0.242</v>
       </c>
       <c r="D19" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E19" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F19" t="n">
-        <v>0.402</v>
+        <v>0.375</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="H19" t="n">
-        <v>0.402</v>
+        <v>0.384</v>
       </c>
       <c r="I19" t="n">
-        <v>0.402</v>
+        <v>0.384</v>
       </c>
       <c r="J19" t="n">
-        <v>0.402</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001</v>
+        <v>0.242</v>
       </c>
       <c r="D20" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E20" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F20" t="n">
-        <v>0.402</v>
+        <v>0.375</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="H20" t="n">
-        <v>0.402</v>
+        <v>0.384</v>
       </c>
       <c r="I20" t="n">
-        <v>0.402</v>
+        <v>0.384</v>
       </c>
       <c r="J20" t="n">
-        <v>0.402</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001</v>
+        <v>0.229</v>
       </c>
       <c r="D21" t="n">
-        <v>0.384</v>
+        <v>0.356</v>
       </c>
       <c r="E21" t="n">
-        <v>0.384</v>
+        <v>0.356</v>
       </c>
       <c r="F21" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="H21" t="n">
-        <v>0.384</v>
+        <v>0.366</v>
       </c>
       <c r="I21" t="n">
-        <v>0.384</v>
+        <v>0.366</v>
       </c>
       <c r="J21" t="n">
-        <v>0.385</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.002</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1189,96 +1189,96 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="D23" t="n">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="E23" t="n">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="F23" t="n">
-        <v>0.204</v>
+        <v>0.169</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="H23" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I23" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J23" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="D24" t="n">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="E24" t="n">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="F24" t="n">
-        <v>0.204</v>
+        <v>0.169</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="H24" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I24" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J24" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="D25" t="n">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="E25" t="n">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="F25" t="n">
-        <v>0.204</v>
+        <v>0.169</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="H25" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I25" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J25" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="26">
@@ -1289,256 +1289,256 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.044</v>
-      </c>
       <c r="E26" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.029</v>
-      </c>
       <c r="I26" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.003</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E27" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F27" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001</v>
+        <v>0.389</v>
       </c>
       <c r="H27" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
       <c r="I27" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
       <c r="J27" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.003</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E28" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F28" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001</v>
+        <v>0.389</v>
       </c>
       <c r="H28" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
       <c r="I28" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
       <c r="J28" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.003</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E29" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F29" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001</v>
+        <v>0.389</v>
       </c>
       <c r="H29" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
       <c r="I29" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
       <c r="J29" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.002</v>
+        <v>0.528</v>
       </c>
       <c r="D30" t="n">
-        <v>0.223</v>
+        <v>0.187</v>
       </c>
       <c r="E30" t="n">
-        <v>0.223</v>
+        <v>0.187</v>
       </c>
       <c r="F30" t="n">
-        <v>0.214</v>
+        <v>0.179</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="H30" t="n">
-        <v>0.146</v>
+        <v>0.12</v>
       </c>
       <c r="I30" t="n">
-        <v>0.146</v>
+        <v>0.12</v>
       </c>
       <c r="J30" t="n">
-        <v>0.146</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.003</v>
+        <v>0.764</v>
       </c>
       <c r="D31" t="n">
-        <v>0.312</v>
+        <v>0.28</v>
       </c>
       <c r="E31" t="n">
-        <v>0.312</v>
+        <v>0.28</v>
       </c>
       <c r="F31" t="n">
-        <v>0.299</v>
+        <v>0.268</v>
       </c>
       <c r="G31" t="n">
-        <v>0.001</v>
+        <v>0.294</v>
       </c>
       <c r="H31" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I31" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J31" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.003</v>
+        <v>0.764</v>
       </c>
       <c r="D32" t="n">
-        <v>0.312</v>
+        <v>0.28</v>
       </c>
       <c r="E32" t="n">
-        <v>0.312</v>
+        <v>0.28</v>
       </c>
       <c r="F32" t="n">
-        <v>0.299</v>
+        <v>0.268</v>
       </c>
       <c r="G32" t="n">
-        <v>0.001</v>
+        <v>0.294</v>
       </c>
       <c r="H32" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I32" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J32" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.003</v>
+        <v>0.764</v>
       </c>
       <c r="D33" t="n">
-        <v>0.312</v>
+        <v>0.28</v>
       </c>
       <c r="E33" t="n">
-        <v>0.312</v>
+        <v>0.28</v>
       </c>
       <c r="F33" t="n">
-        <v>0.299</v>
+        <v>0.268</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001</v>
+        <v>0.294</v>
       </c>
       <c r="H33" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I33" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J33" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="34">
@@ -1549,256 +1549,256 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.647</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E35" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F35" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G35" t="n">
-        <v>0.648</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
       <c r="I35" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
       <c r="J35" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.647</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E36" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F36" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G36" t="n">
-        <v>0.648</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
       <c r="I36" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
       <c r="J36" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.647</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="E37" t="n">
-        <v>0.402</v>
+        <v>0.374</v>
       </c>
       <c r="F37" t="n">
-        <v>0.384</v>
+        <v>0.357</v>
       </c>
       <c r="G37" t="n">
-        <v>0.648</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
       <c r="I37" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
       <c r="J37" t="n">
-        <v>0.133</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0.441</v>
       </c>
       <c r="D39" t="n">
-        <v>0.62</v>
+        <v>0.233</v>
       </c>
       <c r="E39" t="n">
-        <v>0.62</v>
+        <v>0.233</v>
       </c>
       <c r="F39" t="n">
-        <v>0.594</v>
+        <v>0.223</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.654</v>
       </c>
       <c r="H39" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I39" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J39" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0.441</v>
       </c>
       <c r="D40" t="n">
-        <v>0.62</v>
+        <v>0.233</v>
       </c>
       <c r="E40" t="n">
-        <v>0.62</v>
+        <v>0.233</v>
       </c>
       <c r="F40" t="n">
-        <v>0.594</v>
+        <v>0.223</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0.654</v>
       </c>
       <c r="H40" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I40" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J40" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0.441</v>
       </c>
       <c r="D41" t="n">
-        <v>0.62</v>
+        <v>0.233</v>
       </c>
       <c r="E41" t="n">
-        <v>0.62</v>
+        <v>0.233</v>
       </c>
       <c r="F41" t="n">
-        <v>0.594</v>
+        <v>0.223</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0.654</v>
       </c>
       <c r="H41" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="I41" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
       <c r="J41" t="n">
-        <v>0.205</v>
+        <v>0.181</v>
       </c>
     </row>
   </sheetData>
